--- a/docs/MindX 6.0.RC3 通信矩阵.xlsx
+++ b/docs/MindX 6.0.RC3 通信矩阵.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7000" tabRatio="530"/>
+    <workbookView windowHeight="17250" tabRatio="530"/>
   </bookViews>
   <sheets>
     <sheet name="MindX SDK" sheetId="9" r:id="rId1"/>
@@ -629,8 +629,8 @@
     <t>LCCL集合通信训练业务所在的服务器</t>
   </si>
   <si>
-    <t>动态端口
-10067~60999</t>
+    <t>用户可配置，默认10067，取值范围
+0~65535</t>
   </si>
   <si>
     <t>LCCL选择一个AI server作为TCP服务器，主动监听响应其他AI server的socket建链请求，连接后进行TCP数据传输，实现集群计算资源信息的收集和分发。
@@ -647,7 +647,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -661,31 +661,15 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <name val="Cambria"/>
       <charset val="134"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -695,7 +679,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -703,7 +687,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -711,14 +695,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -726,7 +710,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -734,7 +718,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -742,7 +726,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -750,7 +734,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -758,14 +742,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -773,7 +757,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -781,7 +765,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -789,14 +773,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -804,42 +788,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -854,6 +838,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -861,11 +850,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
@@ -1209,19 +1193,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1230,153 +1226,141 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1401,72 +1385,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="59">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
     <cellStyle name="0,0_x000d__x000a_NA_x000d__x000a_" xfId="49"/>
     <cellStyle name="0,0_x000d__x000a_NA_x000d__x000a_ 2 2" xfId="50"/>
     <cellStyle name="0,0_x000d__x000a_NA_x000d__x000a_ 2 2 2" xfId="51"/>
@@ -1806,26 +1784,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="38.7545454545455" customWidth="1"/>
-    <col min="2" max="2" width="31.1272727272727" customWidth="1"/>
+    <col min="1" max="1" width="38.7583333333333" customWidth="1"/>
+    <col min="2" max="2" width="31.125" customWidth="1"/>
     <col min="3" max="3" width="21.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="33.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.7545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.7583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
-    <col min="7" max="7" width="23.1272727272727" style="1" customWidth="1"/>
-    <col min="8" max="8" width="37.6272727272727" customWidth="1"/>
+    <col min="7" max="7" width="23.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.625" customWidth="1"/>
     <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="8.12727272727273" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.125" style="1" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="7.87272727272727" customWidth="1"/>
-    <col min="14" max="14" width="10.2545454545455" customWidth="1"/>
-    <col min="15" max="15" width="22.1272727272727" customWidth="1"/>
+    <col min="13" max="13" width="7.875" customWidth="1"/>
+    <col min="14" max="14" width="10.2583333333333" customWidth="1"/>
+    <col min="15" max="15" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:15">
+    <row r="1" ht="25.5" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1900,22 +1878,22 @@
       <c r="I2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1947,22 +1925,22 @@
       <c r="I3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1994,22 +1972,22 @@
       <c r="I4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="N4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2041,22 +2019,22 @@
       <c r="I5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2088,22 +2066,22 @@
       <c r="I6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2135,26 +2113,26 @@
       <c r="I7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="56" spans="1:15">
+    <row r="8" ht="54" spans="1:15">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -2191,13 +2169,13 @@
       <c r="L8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2205,46 +2183,46 @@
       <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>52</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="11" t="s">
+      <c r="N9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O9" s="12" t="s">
+      <c r="O9" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2252,46 +2230,46 @@
       <c r="A10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="9" t="s">
         <v>21</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2299,46 +2277,46 @@
       <c r="A11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="9" t="s">
         <v>52</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2349,7 +2327,7 @@
       <c r="B12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2358,7 +2336,7 @@
       <c r="E12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="9" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -2373,19 +2351,19 @@
       <c r="J12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="O12" s="12" t="s">
+      <c r="O12" s="10" t="s">
         <v>26</v>
       </c>
     </row>
